--- a/frontend/test_data/header_detection/No_Header_Test.xlsx
+++ b/frontend/test_data/header_detection/No_Header_Test.xlsx
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:M2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -468,18 +468,27 @@
         <v>Consistent String Signal</v>
       </c>
       <c r="F1" t="str">
+        <v>Consistent Numeric Signal</v>
+      </c>
+      <c r="G1" t="str">
         <v>Pure Data Penalty</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>Numeric Data Penalty</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Pivoted Series Bonus</v>
+      </c>
+      <c r="J1" t="str">
         <v>100% String Bonus</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>Unique Values Rule</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>Orphan Header Penalty</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>TOTAL SCORE</v>
       </c>
     </row>
@@ -497,7 +506,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -506,18 +515,27 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>-20</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>37</v>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/test_data/header_detection/No_Header_Test.xlsx
+++ b/frontend/test_data/header_detection/No_Header_Test.xlsx
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:O2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -459,37 +459,43 @@
         <v>Row Preview</v>
       </c>
       <c r="C1" t="str">
-        <v>Density Bonus</v>
+        <v>Pillar 1: Density (%)</v>
       </c>
       <c r="D1" t="str">
-        <v>Data Boundary Signal</v>
+        <v>Pillar 2: Boundary (%)</v>
       </c>
       <c r="E1" t="str">
-        <v>Consistent String Signal</v>
+        <v>Pillar 3: Consistency (%)</v>
       </c>
       <c r="F1" t="str">
-        <v>Consistent Numeric Signal</v>
+        <v>Pillar 4: Traits (%)</v>
       </c>
       <c r="G1" t="str">
         <v>Pure Data Penalty</v>
       </c>
       <c r="H1" t="str">
-        <v>Numeric Data Penalty</v>
+        <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Pivoted Series Bonus</v>
+        <v>Search Booster (Pivoted)</v>
       </c>
       <c r="J1" t="str">
-        <v>100% String Bonus</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Unique Values Rule</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="L1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL SCORE</v>
+        <v>TOTAL RAW SCORE</v>
+      </c>
+      <c r="N1" t="str">
+        <v>NORMALIZED SCORE (%)</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Unsupported Pivoted Penalty</v>
       </c>
     </row>
     <row r="2">
@@ -500,42 +506,48 @@
         <v>["V001","Acme Corp","Austin","TX","5000","6000"]</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>-34</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>9</v>
+      <c r="O2">
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/frontend/test_data/header_detection/No_Header_Test.xlsx
+++ b/frontend/test_data/header_detection/No_Header_Test.xlsx
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:M2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -477,25 +477,19 @@
         <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Search Booster (Pivoted)</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="J1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Duplicates Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="L1" t="str">
-        <v>FILLED CELLS</v>
+        <v>TOTAL RAW SCORE</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL RAW SCORE</v>
-      </c>
-      <c r="N1" t="str">
         <v>NORMALIZED SCORE (%)</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Unsupported Pivoted Penalty</v>
       </c>
     </row>
     <row r="2">
@@ -512,7 +506,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -521,33 +515,27 @@
         <v>0</v>
       </c>
       <c r="H2">
+        <v>-30</v>
+      </c>
+      <c r="I2">
         <v>0</v>
-      </c>
-      <c r="I2">
-        <v>20</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M2">
-        <v>-34</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>-100</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
   </ignoredErrors>
 </worksheet>
 </file>